--- a/yellow-server/data/results/merge.xlsx
+++ b/yellow-server/data/results/merge.xlsx
@@ -555,16 +555,16 @@
         <v>1</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="str">
-        <v/>
+        <v>- 2025-05-14 18:15:33-2025-05-15 13:10:14: 张三 和 孙一(男）证件号：310227199810011020在松江商务宾馆101房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y2" t="str">
-        <v/>
+        <v>- 2025-05-14 18:15:33-2025-05-15 13:10:14 张三 入住 松江商务宾馆101房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z2" t="str">
         <v>小区</v>
@@ -576,7 +576,7 @@
         <v>是</v>
       </c>
       <c r="AC2" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -599,7 +599,7 @@
         <v>新桥镇新中街10000号10002室</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="str">
         <v>高</v>
@@ -645,16 +645,16 @@
         <v>1</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="str">
-        <v/>
+        <v>- 2025-03-26 13:16:38-2025-03-26 15:46:44: 老王 和 孙二(男）证件号：310227199810011021在松江商务宾馆102房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y3" t="str">
-        <v/>
+        <v>- 2025-03-26 13:16:38-2025-03-26 15:46:44 老王 入住 松江商务宾馆102房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z3" t="str">
         <v>场所</v>
@@ -666,7 +666,7 @@
         <v>是</v>
       </c>
       <c r="AC3" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -735,16 +735,16 @@
         <v>1</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="str">
-        <v/>
+        <v>- 2025-04-01 11:42:49-2025-04-01 15:44:58: 老张 和 孙三(男）证件号：310227199810011022在松江商务宾馆103房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y4" t="str">
-        <v/>
+        <v>- 2025-04-01 11:42:49-2025-04-01 15:44:58 老张 入住 松江商务宾馆103房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z4" t="str">
         <v>小区</v>
@@ -756,7 +756,7 @@
         <v>是</v>
       </c>
       <c r="AC4" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
@@ -825,16 +825,16 @@
         <v>1</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="str">
-        <v/>
+        <v>- 2025-05-15 21:29:24-2025-05-17 11:21:31: 老李 和 孙四(男）证件号：310227199810011023在松江商务宾馆104房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y5" t="str">
-        <v/>
+        <v>- 2025-05-15 21:29:24-2025-05-17 11:21:31 老李 入住 松江商务宾馆104房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z5" t="str">
         <v>小区</v>
@@ -846,7 +846,7 @@
         <v>是</v>
       </c>
       <c r="AC5" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
@@ -915,16 +915,16 @@
         <v>1</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="str">
-        <v/>
+        <v>- 2025-04-19 05:53:33- : 小王 和 孙五(男）证件号：310227199810011024在松江商务宾馆105房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y6" t="str">
-        <v/>
+        <v>- 2025-04-19 05:53:33-  小王 入住 松江商务宾馆105房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z6" t="str">
         <v>小区</v>
@@ -936,7 +936,7 @@
         <v>是</v>
       </c>
       <c r="AC6" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
@@ -959,10 +959,10 @@
         <v>新桥镇新中街10000号10006室</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="str">
-        <v>低</v>
+        <v>中</v>
       </c>
       <c r="I7" t="str">
         <v>桃园路90号</v>
@@ -987,7 +987,7 @@
         <v>2025年5月8日，我所民警在侦办案件中，通过深挖线索发现松江区桃园路90号小李等人有卖淫嫖娼的行为。</v>
       </c>
       <c r="P7" t="str">
-        <v>- 20251001121212 - 商品: &lt;span style='color:darkgreen'&gt;[福人]金刚藤胶囊0.5g*42粒/盒×1;[可孚]阴道冲洗器(中号伸缩式KF-S01)150ml/袋×2;[何医生]妇洁舒冲洗器50ml/盒×1;&lt;/span&gt; - 收货地址：松江公寓 (127)</v>
+        <v>- 20251001121212 - 商品: &lt;span style='color:darkorange'&gt;[福人]金刚藤胶囊0.5g*42粒/盒×1;[可孚]阴道冲洗器(中号伸缩式KF-S01)150ml/袋×2;[何医生]妇洁舒冲洗器50ml/盒×1;&lt;/span&gt; - 收货地址：松江公寓 (127)</v>
       </c>
       <c r="Q7" t="str">
         <v>上海电子商务有限公司</v>
@@ -1005,16 +1005,16 @@
         <v>1</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="str">
-        <v/>
+        <v>- 2025-06-15 04:49:04-2025-06-15 16:58:54: 小李 和 孙六(男）证件号：310227199810011025在松江商务宾馆106房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y7" t="str">
-        <v/>
+        <v>- 2025-06-15 04:49:04-2025-06-15 16:58:54 小李 入住 松江商务宾馆106房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z7" t="str">
         <v>小区</v>
@@ -1026,7 +1026,7 @@
         <v>是</v>
       </c>
       <c r="AC7" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
@@ -1052,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="str">
-        <v>低</v>
+        <v>中</v>
       </c>
       <c r="I8" t="str">
         <v>桃园路90号</v>
@@ -1077,7 +1077,7 @@
         <v>2025年5月14日，我所民警接线索举报称上海市松江区桃园路90号有卖淫嫖娼的情况，遂至上址检查，并经出示证件将相关人员传唤至所作进一步调查。</v>
       </c>
       <c r="P8" t="str">
-        <v>- 20251001121212 - 商品: &lt;span style='color:darkgreen'&gt;[福人]金刚藤胶囊0.5g*42粒/盒×1;[可孚]阴道冲洗器(中号伸缩式KF-S01)150ml/袋×2;[何医生]妇洁舒冲洗器50ml/盒×1;&lt;/span&gt; - 收货地址：松江公寓 (128)</v>
+        <v>- 20251001121212 - 商品: &lt;span style='color:darkorange'&gt;[福人]金刚藤胶囊0.5g*42粒/盒×1;[可孚]阴道冲洗器(中号伸缩式KF-S01)150ml/袋×2;[何医生]妇洁舒冲洗器50ml/盒×1;&lt;/span&gt; - 收货地址：松江公寓 (128)</v>
       </c>
       <c r="Q8" t="str">
         <v>上海电子商务有限公司</v>
@@ -1095,16 +1095,16 @@
         <v>1</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="str">
-        <v/>
+        <v>- 2025-05-27 22:28:33-2025-05-29 14:38:50: 小胡 和 孙七(男）证件号：310227199810011026在松江商务宾馆107房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y8" t="str">
-        <v/>
+        <v>- 2025-05-27 22:28:33-2025-05-29 14:38:50 小胡 入住 松江商务宾馆107房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z8" t="str">
         <v>小区</v>
@@ -1116,7 +1116,7 @@
         <v>是</v>
       </c>
       <c r="AC8" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
@@ -1139,7 +1139,7 @@
         <v>新桥镇新中街10000号10008室</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="str">
         <v>中</v>
@@ -1185,16 +1185,16 @@
         <v>1</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="str">
-        <v/>
+        <v>- 2025-04-14 22:22:42- : 小刚 和 孙八(男）证件号：310227199810011027在松江商务宾馆108房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y9" t="str">
-        <v/>
+        <v>- 2025-04-14 22:22:42-  小刚 入住 松江商务宾馆108房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z9" t="str">
         <v>小区</v>
@@ -1206,7 +1206,7 @@
         <v>是</v>
       </c>
       <c r="AC9" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
@@ -1229,7 +1229,7 @@
         <v>新桥镇新中街10000号10009室</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="str">
         <v>中</v>
@@ -1275,16 +1275,16 @@
         <v>1</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="str">
-        <v/>
+        <v>- 2025-05-20 21:34:39-2025-05-21 22:53:18: 小金 和 孙九(男）证件号：310227199810011028在松江商务宾馆109房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y10" t="str">
-        <v/>
+        <v>- 2025-05-20 21:34:39-2025-05-21 22:53:18 小金 入住 松江商务宾馆109房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z10" t="str">
         <v>小区</v>
@@ -1296,7 +1296,7 @@
         <v>是</v>
       </c>
       <c r="AC10" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="11" xml:space="preserve">
@@ -1365,16 +1365,16 @@
         <v>1</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="str">
-        <v/>
+        <v>- 2025-05-20 21:34:39-2025-05-21 22:53:18: 小钱 和 孙十(男）证件号：310227199810011029在松江商务宾馆110房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y11" t="str">
-        <v/>
+        <v>- 2025-05-20 21:34:39-2025-05-21 22:53:18 小钱 入住 松江商务宾馆110房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z11" t="str">
         <v>场所</v>
@@ -1386,7 +1386,7 @@
         <v>是</v>
       </c>
       <c r="AC11" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
   </sheetData>
